--- a/static/excel/TSM_model.xlsx
+++ b/static/excel/TSM_model.xlsx
@@ -7835,16 +7835,16 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B46" s="55">
-        <f>B8*B29+B9*B39*(1-B43)</f>
+        <f>MAX(0.085, B8*B29+B9*B39*(1-B43))</f>
         <v/>
       </c>
       <c r="C46" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8210,10 +8210,10 @@
         <v>0.3665</v>
       </c>
       <c r="H7" s="72" t="n">
-        <v>0.2704</v>
+        <v>0.2718</v>
       </c>
       <c r="I7" s="72" t="n">
-        <v>0.2292</v>
+        <v>0.2307</v>
       </c>
       <c r="J7" s="73">
         <f>I7</f>
@@ -8557,13 +8557,13 @@
         <v/>
       </c>
       <c r="G15" s="78" t="n">
-        <v>5258970.2</v>
+        <v>5258968.2</v>
       </c>
       <c r="H15" s="78" t="n">
-        <v>6680999</v>
+        <v>6688211.7</v>
       </c>
       <c r="I15" s="78" t="n">
-        <v>8212028.2</v>
+        <v>8231278.2</v>
       </c>
       <c r="J15" s="79">
         <f>I15*(1+J7)</f>
@@ -8591,22 +8591,22 @@
       </c>
       <c r="G16" s="83" t="inlineStr">
         <is>
-          <t>5,036,380 — 5,457,839</t>
+          <t>5,036,378 — 5,457,837</t>
         </is>
       </c>
       <c r="H16" s="83" t="inlineStr">
         <is>
-          <t>6,384,609 — 7,223,891</t>
+          <t>6,391,502 — 7,231,690</t>
         </is>
       </c>
       <c r="I16" s="83" t="inlineStr">
         <is>
-          <t>7,128,985 — 8,717,567</t>
+          <t>7,138,763 — 8,729,618</t>
         </is>
       </c>
       <c r="J16" s="83" t="inlineStr">
         <is>
-          <t>6,877,149 — 8,409,614</t>
+          <t>6,870,477 — 8,401,545</t>
         </is>
       </c>
       <c r="K16" s="84" t="inlineStr">
@@ -8757,13 +8757,13 @@
         <v/>
       </c>
       <c r="G20" s="78" t="n">
-        <v>3677721.2</v>
+        <v>3677719.8</v>
       </c>
       <c r="H20" s="78" t="n">
-        <v>4672179.3</v>
+        <v>4677223.3</v>
       </c>
       <c r="I20" s="78" t="n">
-        <v>5742864</v>
+        <v>5756326</v>
       </c>
       <c r="J20" s="79">
         <f>J15*J8</f>
@@ -8791,22 +8791,22 @@
       </c>
       <c r="G21" s="83" t="inlineStr">
         <is>
-          <t>3,522,059 — 3,816,795</t>
+          <t>3,522,058 — 3,816,793</t>
         </is>
       </c>
       <c r="H21" s="83" t="inlineStr">
         <is>
-          <t>4,464,907 — 5,051,837</t>
+          <t>4,469,727 — 5,057,290</t>
         </is>
       </c>
       <c r="I21" s="83" t="inlineStr">
         <is>
-          <t>4,985,466 — 6,096,399</t>
+          <t>4,992,304 — 6,104,826</t>
         </is>
       </c>
       <c r="J21" s="83" t="inlineStr">
         <is>
-          <t>4,809,352 — 5,881,040</t>
+          <t>4,804,686 — 5,875,397</t>
         </is>
       </c>
       <c r="K21" s="84" t="inlineStr">
@@ -10091,7 +10091,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="116" t="inlineStr">
         <is>
-          <t>JS SCORECARD — TSM  |  Master Prompt v2  |  23 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — TSM  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
       </c>
       <c r="D22" s="132" t="inlineStr">
         <is>
-          <t>Current 28.5x  |  5yr avg 23.6x  |  Sector median 80.5x  |  DCF-implied 29.1x [ref only — not used as benchmark]  [+21% vs benchmark]  [trail=3.68 | no_fwd_data(fallback) | abs=4.0 → blended 40/40/20=3.74]  PEG≈147.31 (trailing_pe=28.5x / rev_cagr=19%, revenue proxy)</t>
+          <t>Current 28.5x  |  5yr avg 23.6x  |  Sector median 80.5x  [+21% vs benchmark]  [trail=3.68 | fwd_pe=0.8x→10.00 | abs=4.5 → blended 40/40/20=6.37]  PEG=1.61 (fwd_pe=0.8x / eps_growth=50%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
       <c r="E22" s="133" t="inlineStr">
@@ -10617,7 +10617,7 @@
         </is>
       </c>
       <c r="F22" s="134" t="n">
-        <v>3.74</v>
+        <v>6.87</v>
       </c>
       <c r="G22" s="135">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="H22" s="136" t="inlineStr">
         <is>
-          <t>Current 28.5x  |  5yr avg 23.6x  |  Sector median 80.5x  |  DCF-implied 29.1x [ref only — not used as benchmark]  [+21% vs benchmark]  [trail=3.68 | no_fwd_data(fallback) | abs=4.0 → blended 40/40/20=3.74]  PEG≈147.31 (trailing_pe=28.5x / rev_cagr=19%, revenue proxy)</t>
+          <t>Current 28.5x  |  5yr avg 23.6x  |  Sector median 80.5x  [+21% vs benchmark]  [trail=3.68 | fwd_pe=0.8x→10.00 | abs=4.5 → blended 40/40/20=6.37]  PEG=1.61 (fwd_pe=0.8x / eps_growth=50%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="D23" s="132" t="inlineStr">
         <is>
-          <t>Current 45.0x  |  5yr avg 45.9x  |  Sector median 51.8x  |  DCF-implied 46.1x [ref only — not used as benchmark]  [-2% vs benchmark]  [trail=7.29 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=6.14]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
+          <t>Current 45.0x  |  5yr avg 45.9x  |  Sector median 51.8x  [-2% vs benchmark]  [trail=7.29 | fwd_pfcf=1.4x→10.00 | abs=1.5 → blended 40/40/20=7.22]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="137" t="inlineStr">
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="F23" s="134" t="n">
-        <v>5.64</v>
+        <v>6.72</v>
       </c>
       <c r="G23" s="135">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="H23" s="136" t="inlineStr">
         <is>
-          <t>Current 45.0x  |  5yr avg 45.9x  |  Sector median 51.8x  |  DCF-implied 46.1x [ref only — not used as benchmark]  [-2% vs benchmark]  [trail=7.29 | no_fwd_data(fallback) | abs=1.5 → blended 40/40/20=6.14]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
+          <t>Current 45.0x  |  5yr avg 45.9x  |  Sector median 51.8x  [-2% vs benchmark]  [trail=7.29 | fwd_pfcf=1.4x→10.00 | abs=1.5 → blended 40/40/20=7.22]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
         </is>
       </c>
     </row>

--- a/static/excel/TSM_model.xlsx
+++ b/static/excel/TSM_model.xlsx
@@ -7439,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7668,25 +7668,27 @@
       </c>
       <c r="B32" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B33" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="n">
+        <v>0.0496</v>
+      </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A2CAAEY — AA</t>
         </is>
       </c>
     </row>
@@ -7727,11 +7729,11 @@
         </is>
       </c>
       <c r="B36" s="46" t="n">
-        <v>0.05110000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="C36" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.54%</t>
+          <t>Rf 4.56% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7770,11 +7772,11 @@
         </is>
       </c>
       <c r="B39" s="48" t="n">
-        <v>0.0256</v>
+        <v>0.0335</v>
       </c>
       <c r="C39" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -8601,12 +8603,12 @@
       </c>
       <c r="I16" s="83" t="inlineStr">
         <is>
-          <t>7,138,763 — 8,729,618</t>
+          <t>7,138,800 — 8,729,618</t>
         </is>
       </c>
       <c r="J16" s="83" t="inlineStr">
         <is>
-          <t>6,870,477 — 8,401,545</t>
+          <t>6,870,512 — 8,401,545</t>
         </is>
       </c>
       <c r="K16" s="84" t="inlineStr">
@@ -8801,12 +8803,12 @@
       </c>
       <c r="I21" s="83" t="inlineStr">
         <is>
-          <t>4,992,304 — 6,104,826</t>
+          <t>4,992,330 — 6,104,827</t>
         </is>
       </c>
       <c r="J21" s="83" t="inlineStr">
         <is>
-          <t>4,804,686 — 5,875,397</t>
+          <t>4,804,710 — 5,875,398</t>
         </is>
       </c>
       <c r="K21" s="84" t="inlineStr">
@@ -10091,7 +10093,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="116" t="inlineStr">
         <is>
-          <t>JS SCORECARD — TSM  |  Master Prompt v2  |  25 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — TSM  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10608,16 +10610,16 @@
       </c>
       <c r="D22" s="132" t="inlineStr">
         <is>
-          <t>Current 28.5x  |  5yr avg 23.6x  |  Sector median 80.5x  [+21% vs benchmark]  [trail=3.68 | fwd_pe=0.8x→10.00 | abs=4.5 → blended 40/40/20=6.37]  PEG=1.61 (fwd_pe=0.8x / eps_growth=50%)  [revision:Strong upgrade cycle→+0.50]</t>
-        </is>
-      </c>
-      <c r="E22" s="133" t="inlineStr">
-        <is>
-          <t>MOD-LOW</t>
+          <t>Fwd P/E 0.8x (scoring basis)  |  5yr avg 24.6x  |  Sector median 80.5x  [-97% vs benchmark]  [trail=10.00 | fwd_pe=0.8x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=1.61 (fwd_pe=0.8x / eps_growth=50%)  [revision:Strong upgrade cycle→+0.50]</t>
+        </is>
+      </c>
+      <c r="E22" s="138" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F22" s="134" t="n">
-        <v>6.87</v>
+        <v>10.9</v>
       </c>
       <c r="G22" s="135">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10625,7 +10627,7 @@
       </c>
       <c r="H22" s="136" t="inlineStr">
         <is>
-          <t>Current 28.5x  |  5yr avg 23.6x  |  Sector median 80.5x  [+21% vs benchmark]  [trail=3.68 | fwd_pe=0.8x→10.00 | abs=4.5 → blended 40/40/20=6.37]  PEG=1.61 (fwd_pe=0.8x / eps_growth=50%)  [revision:Strong upgrade cycle→+0.50]</t>
+          <t>Fwd P/E 0.8x (scoring basis)  |  5yr avg 24.6x  |  Sector median 80.5x  [-97% vs benchmark]  [trail=10.00 | fwd_pe=0.8x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=1.61 (fwd_pe=0.8x / eps_growth=50%)  [revision:Strong upgrade cycle→+0.50]</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10647,7 @@
       </c>
       <c r="D23" s="132" t="inlineStr">
         <is>
-          <t>Current 45.0x  |  5yr avg 45.9x  |  Sector median 51.8x  [-2% vs benchmark]  [trail=7.29 | fwd_pfcf=1.4x→10.00 | abs=1.5 → blended 40/40/20=7.22]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
+          <t>Current 45.0x  |  5yr avg 45.7x  |  Sector median 51.8x  [-2% vs benchmark]  [trail=7.23 | fwd_pfcf=1.4x→10.00 | abs=1.5 → blended 40/40/20=7.19]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
         </is>
       </c>
       <c r="E23" s="137" t="inlineStr">
@@ -10654,7 +10656,7 @@
         </is>
       </c>
       <c r="F23" s="134" t="n">
-        <v>6.72</v>
+        <v>6.69</v>
       </c>
       <c r="G23" s="135">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10662,7 +10664,7 @@
       </c>
       <c r="H23" s="136" t="inlineStr">
         <is>
-          <t>Current 45.0x  |  5yr avg 45.9x  |  Sector median 51.8x  [-2% vs benchmark]  [trail=7.29 | fwd_pfcf=1.4x→10.00 | abs=1.5 → blended 40/40/20=7.22]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
+          <t>Current 45.0x  |  5yr avg 45.7x  |  Sector median 51.8x  [-2% vs benchmark]  [trail=7.23 | fwd_pfcf=1.4x→10.00 | abs=1.5 → blended 40/40/20=7.19]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
         </is>
       </c>
     </row>

--- a/static/excel/TSM_model.xlsx
+++ b/static/excel/TSM_model.xlsx
@@ -7439,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.04559999999999999</v>
+        <v>0.0446</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-22</t>
+          <t>FRED series DGS10  |  latest: 2026-06-18</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0456</v>
+        <v>0.0446</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7540,11 +7540,11 @@
         </is>
       </c>
       <c r="B20" s="50" t="n">
-        <v>2.19</v>
+        <v>2.228</v>
       </c>
       <c r="C20" s="44" t="inlineStr">
         <is>
-          <t xml:space="preserve">AMD: 2.399  |  INTC: 2.19  |  QCOM: 1.493  |  AVGO: </t>
+          <t>AMD: 2.492  |  INTC: 2.228  |  QCOM: 1.596  |  AVGO:</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="B21" s="51" t="n">
-        <v>1.564</v>
+        <v>1.574</v>
       </c>
       <c r="C21" s="49" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="B33" s="46" t="n">
-        <v>0.0496</v>
+        <v>0.0498</v>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
@@ -7729,11 +7729,11 @@
         </is>
       </c>
       <c r="B36" s="46" t="n">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="C36" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.56% + spread 0.54%</t>
+          <t>Rf 4.46% + spread 0.54%</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7772,7 @@
         </is>
       </c>
       <c r="B39" s="48" t="n">
-        <v>0.0335</v>
+        <v>0.0333</v>
       </c>
       <c r="C39" s="49" t="inlineStr">
         <is>
@@ -8209,13 +8209,13 @@
         <v/>
       </c>
       <c r="G7" s="72" t="n">
-        <v>0.3665</v>
+        <v>0.3551</v>
       </c>
       <c r="H7" s="72" t="n">
-        <v>0.2718</v>
+        <v>0.2747</v>
       </c>
       <c r="I7" s="72" t="n">
-        <v>0.2307</v>
+        <v>0.2396</v>
       </c>
       <c r="J7" s="73">
         <f>I7</f>
@@ -8559,13 +8559,13 @@
         <v/>
       </c>
       <c r="G15" s="78" t="n">
-        <v>5258968.2</v>
+        <v>5215108.3</v>
       </c>
       <c r="H15" s="78" t="n">
-        <v>6688211.7</v>
+        <v>6647930.2</v>
       </c>
       <c r="I15" s="78" t="n">
-        <v>8231278.2</v>
+        <v>8240663.4</v>
       </c>
       <c r="J15" s="79">
         <f>I15*(1+J7)</f>
@@ -8593,22 +8593,22 @@
       </c>
       <c r="G16" s="83" t="inlineStr">
         <is>
-          <t>5,036,378 — 5,457,837</t>
+          <t>4,993,141 — 5,410,981</t>
         </is>
       </c>
       <c r="H16" s="83" t="inlineStr">
         <is>
-          <t>6,391,502 — 7,231,690</t>
+          <t>6,352,387 — 7,187,434</t>
         </is>
       </c>
       <c r="I16" s="83" t="inlineStr">
         <is>
-          <t>7,138,800 — 8,729,618</t>
+          <t>7,132,810 — 8,721,914</t>
         </is>
       </c>
       <c r="J16" s="83" t="inlineStr">
         <is>
-          <t>6,870,512 — 8,401,545</t>
+          <t>6,789,675 — 8,302,333</t>
         </is>
       </c>
       <c r="K16" s="84" t="inlineStr">
@@ -8759,13 +8759,13 @@
         <v/>
       </c>
       <c r="G20" s="78" t="n">
-        <v>3677719.8</v>
+        <v>3647047.6</v>
       </c>
       <c r="H20" s="78" t="n">
-        <v>4677223.3</v>
+        <v>4649053.5</v>
       </c>
       <c r="I20" s="78" t="n">
-        <v>5756326</v>
+        <v>5762889.2</v>
       </c>
       <c r="J20" s="79">
         <f>J15*J8</f>
@@ -8793,22 +8793,22 @@
       </c>
       <c r="G21" s="83" t="inlineStr">
         <is>
-          <t>3,522,058 — 3,816,793</t>
+          <t>3,491,821 — 3,784,026</t>
         </is>
       </c>
       <c r="H21" s="83" t="inlineStr">
         <is>
-          <t>4,469,727 — 5,057,290</t>
+          <t>4,442,373 — 5,026,341</t>
         </is>
       </c>
       <c r="I21" s="83" t="inlineStr">
         <is>
-          <t>4,992,330 — 6,104,827</t>
+          <t>4,988,141 — 6,099,439</t>
         </is>
       </c>
       <c r="J21" s="83" t="inlineStr">
         <is>
-          <t>4,804,710 — 5,875,398</t>
+          <t>4,748,179 — 5,806,016</t>
         </is>
       </c>
       <c r="K21" s="84" t="inlineStr">
@@ -10093,7 +10093,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="116" t="inlineStr">
         <is>
-          <t>JS SCORECARD — TSM  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Tech Growth</t>
+          <t>JS SCORECARD — TSM  |  Master Prompt v2  |  23 Jun 2026  |  Sector bucket: Tech Growth</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="D9" s="132" t="inlineStr">
         <is>
-          <t>GM 59.9% ✓ (&gt;40%)  |  GM trend +0.3% ✗ (&gt;+1pp)  |  ROIC-WACC +38.7% ✓ (&gt;+5pp)  |  Rev consistency σ=18.1% ✗ (&lt;8%)  [2/4 indicators positive — proxy score]</t>
+          <t>GM 59.9% ✓ (&gt;40%)  |  GM trend +0.3% ✗ (&gt;+1pp)  |  ROIC-WACC +38.4% ✓ (&gt;+5pp)  |  Rev consistency σ=18.1% ✗ (&lt;8%)  [2/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="133" t="inlineStr">
@@ -10243,7 +10243,7 @@
       </c>
       <c r="H9" s="136" t="inlineStr">
         <is>
-          <t>GM 59.9% ✓ (&gt;40%)  |  GM trend +0.3% ✗ (&gt;+1pp)  |  ROIC-WACC +38.7% ✓ (&gt;+5pp)  |  Rev consistency σ=18.1% ✗ (&lt;8%)  [2/4 indicators positive — proxy score]</t>
+          <t>GM 59.9% ✓ (&gt;40%)  |  GM trend +0.3% ✗ (&gt;+1pp)  |  ROIC-WACC +38.4% ✓ (&gt;+5pp)  |  Rev consistency σ=18.1% ✗ (&lt;8%)  [2/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10595,78 +10595,64 @@
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="129" t="inlineStr">
+      <c r="A22" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Valuation vs Median  (P/E)</t>
         </is>
       </c>
-      <c r="B22" s="130" t="inlineStr">
+      <c r="B22" s="122" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C22" s="131" t="n">
+      <c r="C22" s="123" t="n">
         <v>0.1</v>
       </c>
-      <c r="D22" s="132" t="inlineStr">
-        <is>
-          <t>Fwd P/E 0.8x (scoring basis)  |  5yr avg 24.6x  |  Sector median 80.5x  [-97% vs benchmark]  [trail=10.00 | fwd_pe=0.8x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=1.61 (fwd_pe=0.8x / eps_growth=50%)  [revision:Strong upgrade cycle→+0.50]</t>
-        </is>
-      </c>
-      <c r="E22" s="138" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="F22" s="134" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="G22" s="135">
+      <c r="D22" s="124" t="inlineStr">
+        <is>
+          <t>— user input required</t>
+        </is>
+      </c>
+      <c r="E22" s="125" t="n"/>
+      <c r="F22" s="126">
+        <f>IF(E22="HIGH",10,IF(E22="MOD-HIGH",7,IF(E22="MOD-LOW",3,IF(E22="LOW",0,""))))</f>
+        <v/>
+      </c>
+      <c r="G22" s="127">
         <f>IF(F22="",0,C22*F22*10)</f>
         <v/>
       </c>
-      <c r="H22" s="136" t="inlineStr">
-        <is>
-          <t>Fwd P/E 0.8x (scoring basis)  |  5yr avg 24.6x  |  Sector median 80.5x  [-97% vs benchmark]  [trail=10.00 | fwd_pe=0.8x→10.00 | abs=12.0 → blended 40/40/20=10.40]  PEG=1.61 (fwd_pe=0.8x / eps_growth=50%)  [revision:Strong upgrade cycle→+0.50]</t>
-        </is>
-      </c>
+      <c r="H22" s="128" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="129" t="inlineStr">
+      <c r="A23" s="121" t="inlineStr">
         <is>
           <t xml:space="preserve">  Valuation vs Median  (P/FCF)</t>
         </is>
       </c>
-      <c r="B23" s="130" t="inlineStr">
+      <c r="B23" s="122" t="inlineStr">
         <is>
           <t>P4</t>
         </is>
       </c>
-      <c r="C23" s="131" t="n">
+      <c r="C23" s="123" t="n">
         <v>0.1</v>
       </c>
-      <c r="D23" s="132" t="inlineStr">
-        <is>
-          <t>Current 45.0x  |  5yr avg 45.7x  |  Sector median 51.8x  [-2% vs benchmark]  [trail=7.23 | fwd_pfcf=1.4x→10.00 | abs=1.5 → blended 40/40/20=7.19]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
-        </is>
-      </c>
-      <c r="E23" s="137" t="inlineStr">
-        <is>
-          <t>MOD-HIGH</t>
-        </is>
-      </c>
-      <c r="F23" s="134" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="G23" s="135">
+      <c r="D23" s="124" t="inlineStr">
+        <is>
+          <t>— user input required</t>
+        </is>
+      </c>
+      <c r="E23" s="125" t="n"/>
+      <c r="F23" s="126">
+        <f>IF(E23="HIGH",10,IF(E23="MOD-HIGH",7,IF(E23="MOD-LOW",3,IF(E23="LOW",0,""))))</f>
+        <v/>
+      </c>
+      <c r="G23" s="127">
         <f>IF(F23="",0,C23*F23*10)</f>
         <v/>
       </c>
-      <c r="H23" s="136" t="inlineStr">
-        <is>
-          <t>Current 45.0x  |  5yr avg 45.7x  |  Sector median 51.8x  [-2% vs benchmark]  [trail=7.23 | fwd_pfcf=1.4x→10.00 | abs=1.5 → blended 40/40/20=7.19]  [fcf_yield=2.2% vs rf=4.6%  spread=-2.3%→modifier=-0.50]</t>
-        </is>
-      </c>
+      <c r="H23" s="128" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="42" t="n"/>
